--- a/학생부우수자_입결.xlsx
+++ b/학생부우수자_입결.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\대진대_입학상담_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04AF067-9C36-46B9-A110-952A46F124FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04F66A2-4C84-40E0-AD2E-5EDBAECC6DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{333CE5E8-D45C-448F-B07C-A850148192AA}"/>
+    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{333CE5E8-D45C-448F-B07C-A850148192AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -920,16 +920,13 @@
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -941,8 +938,11 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1290,23 +1290,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
       <c r="Q1" t="s">
         <v>73</v>
       </c>
@@ -1321,41 +1321,41 @@
       <c r="C2" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="30" t="s">
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="31" t="s">
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="32" t="s">
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="26" t="s">
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="27" t="s">
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="28" t="s">
+      <c r="T2" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="U2" s="28" t="s">
+      <c r="U2" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="V2" s="28" t="s">
+      <c r="V2" s="33" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1408,10 +1408,10 @@
       <c r="R3" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="S3" s="27"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="33"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="33"/>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="20">
@@ -1459,13 +1459,13 @@
       <c r="O4" s="8">
         <v>7.2</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="26">
         <v>3.89</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="26">
         <v>3.58</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="26">
         <v>3.3</v>
       </c>
       <c r="S4" s="25" t="s">
@@ -1525,13 +1525,13 @@
       <c r="O5" s="11">
         <v>6.8</v>
       </c>
-      <c r="P5" s="33">
+      <c r="P5" s="26">
         <v>3.05</v>
       </c>
-      <c r="Q5" s="33">
+      <c r="Q5" s="26">
         <v>2.79</v>
       </c>
-      <c r="R5" s="33">
+      <c r="R5" s="26">
         <v>2.33</v>
       </c>
       <c r="S5" s="25" t="s">
@@ -1591,13 +1591,13 @@
       <c r="O6" s="8">
         <v>9.6</v>
       </c>
-      <c r="P6" s="33">
+      <c r="P6" s="26">
         <v>4.1500000000000004</v>
       </c>
-      <c r="Q6" s="33">
+      <c r="Q6" s="26">
         <v>3.45</v>
       </c>
-      <c r="R6" s="33">
+      <c r="R6" s="26">
         <v>2.85</v>
       </c>
       <c r="S6" s="25" t="s">
@@ -1657,14 +1657,14 @@
       <c r="O7" s="11">
         <v>9.4</v>
       </c>
-      <c r="P7" s="33">
-        <v>3.45</v>
-      </c>
-      <c r="Q7" s="33">
-        <v>3.07</v>
-      </c>
-      <c r="R7" s="33">
-        <v>2.74</v>
+      <c r="P7" s="26">
+        <v>4.21</v>
+      </c>
+      <c r="Q7" s="26">
+        <v>3.94</v>
+      </c>
+      <c r="R7" s="26">
+        <v>3.52</v>
       </c>
       <c r="S7" s="25" t="s">
         <v>58</v>
@@ -1723,14 +1723,14 @@
       <c r="O8" s="8">
         <v>14.33</v>
       </c>
-      <c r="P8" s="33">
-        <v>4.21</v>
-      </c>
-      <c r="Q8" s="33">
-        <v>3.94</v>
-      </c>
-      <c r="R8" s="33">
-        <v>3.52</v>
+      <c r="P8" s="26">
+        <v>3.45</v>
+      </c>
+      <c r="Q8" s="26">
+        <v>3.07</v>
+      </c>
+      <c r="R8" s="26">
+        <v>2.74</v>
       </c>
       <c r="S8" s="25" t="s">
         <v>59</v>
@@ -1789,13 +1789,13 @@
       <c r="O9" s="11">
         <v>12.4</v>
       </c>
-      <c r="P9" s="33">
+      <c r="P9" s="26">
         <v>3.28</v>
       </c>
-      <c r="Q9" s="33">
+      <c r="Q9" s="26">
         <v>3.2</v>
       </c>
-      <c r="R9" s="33">
+      <c r="R9" s="26">
         <v>3.07</v>
       </c>
       <c r="S9" s="25" t="s">
@@ -1855,14 +1855,14 @@
       <c r="O10" s="8">
         <v>6.75</v>
       </c>
-      <c r="P10" s="33">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="Q10" s="33">
-        <v>3.93</v>
-      </c>
-      <c r="R10" s="33">
-        <v>3.3</v>
+      <c r="P10" s="26">
+        <v>3.15</v>
+      </c>
+      <c r="Q10" s="26">
+        <v>3.1</v>
+      </c>
+      <c r="R10" s="26">
+        <v>3.02</v>
       </c>
       <c r="S10" s="25" t="s">
         <v>60</v>
@@ -1921,14 +1921,14 @@
       <c r="O11" s="11">
         <v>8.57</v>
       </c>
-      <c r="P11" s="33">
-        <v>3.15</v>
-      </c>
-      <c r="Q11" s="33">
-        <v>3.1</v>
-      </c>
-      <c r="R11" s="33">
-        <v>3.02</v>
+      <c r="P11" s="26">
+        <v>3.96</v>
+      </c>
+      <c r="Q11" s="26">
+        <v>3.8</v>
+      </c>
+      <c r="R11" s="26">
+        <v>3.54</v>
       </c>
       <c r="S11" s="25" t="s">
         <v>57</v>
@@ -1987,14 +1987,14 @@
       <c r="O12" s="8">
         <v>6.25</v>
       </c>
-      <c r="P12" s="33">
-        <v>3.96</v>
-      </c>
-      <c r="Q12" s="33">
-        <v>3.8</v>
-      </c>
-      <c r="R12" s="33">
-        <v>3.54</v>
+      <c r="P12" s="26">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="Q12" s="26">
+        <v>3.93</v>
+      </c>
+      <c r="R12" s="26">
+        <v>3.3</v>
       </c>
       <c r="S12" s="25" t="s">
         <v>57</v>
@@ -2053,14 +2053,14 @@
       <c r="O13" s="11">
         <v>6.63</v>
       </c>
-      <c r="P13" s="33">
-        <v>4.3</v>
-      </c>
-      <c r="Q13" s="33">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="R13" s="33">
-        <v>3.95</v>
+      <c r="P13" s="26">
+        <v>4.21</v>
+      </c>
+      <c r="Q13" s="26">
+        <v>3.65</v>
+      </c>
+      <c r="R13" s="26">
+        <v>3.11</v>
       </c>
       <c r="S13" s="25" t="s">
         <v>57</v>
@@ -2119,13 +2119,13 @@
       <c r="O14" s="8">
         <v>14.13</v>
       </c>
-      <c r="P14" s="33">
+      <c r="P14" s="26">
         <v>3.62</v>
       </c>
-      <c r="Q14" s="33">
+      <c r="Q14" s="26">
         <v>3.3</v>
       </c>
-      <c r="R14" s="33">
+      <c r="R14" s="26">
         <v>3.08</v>
       </c>
       <c r="S14" s="25" t="s">
@@ -2185,14 +2185,14 @@
       <c r="O15" s="11">
         <v>10.25</v>
       </c>
-      <c r="P15" s="33">
-        <v>3.76</v>
-      </c>
-      <c r="Q15" s="33">
-        <v>3.18</v>
-      </c>
-      <c r="R15" s="33">
-        <v>2.65</v>
+      <c r="P15" s="26">
+        <v>4.3</v>
+      </c>
+      <c r="Q15" s="26">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="R15" s="26">
+        <v>3.95</v>
       </c>
       <c r="S15" s="25" t="s">
         <v>58</v>
@@ -2251,14 +2251,14 @@
       <c r="O16" s="8">
         <v>15.5</v>
       </c>
-      <c r="P16" s="33">
-        <v>4.21</v>
-      </c>
-      <c r="Q16" s="33">
-        <v>3.65</v>
-      </c>
-      <c r="R16" s="33">
-        <v>3.11</v>
+      <c r="P16" s="26">
+        <v>3.76</v>
+      </c>
+      <c r="Q16" s="26">
+        <v>3.18</v>
+      </c>
+      <c r="R16" s="26">
+        <v>2.65</v>
       </c>
       <c r="S16" s="25" t="s">
         <v>59</v>
@@ -2317,13 +2317,13 @@
       <c r="O17" s="11">
         <v>6.83</v>
       </c>
-      <c r="P17" s="33">
+      <c r="P17" s="26">
         <v>3.3</v>
       </c>
-      <c r="Q17" s="33">
+      <c r="Q17" s="26">
         <v>3.14</v>
       </c>
-      <c r="R17" s="33">
+      <c r="R17" s="26">
         <v>2.98</v>
       </c>
       <c r="S17" s="25" t="s">
@@ -2385,13 +2385,13 @@
       <c r="O18" s="8">
         <v>8.5</v>
       </c>
-      <c r="P18" s="33">
+      <c r="P18" s="26">
         <v>4.12</v>
       </c>
-      <c r="Q18" s="33">
+      <c r="Q18" s="26">
         <v>3.59</v>
       </c>
-      <c r="R18" s="33">
+      <c r="R18" s="26">
         <v>3.02</v>
       </c>
       <c r="S18" s="25" t="s">
@@ -2451,14 +2451,14 @@
       <c r="O19" s="11">
         <v>15.32</v>
       </c>
-      <c r="P19" s="33">
-        <v>3.9</v>
-      </c>
-      <c r="Q19" s="33">
-        <v>3.28</v>
-      </c>
-      <c r="R19" s="33">
-        <v>2.54</v>
+      <c r="P19" s="26">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Q19" s="26">
+        <v>2.16</v>
+      </c>
+      <c r="R19" s="26">
+        <v>1.91</v>
       </c>
       <c r="S19" s="25" t="s">
         <v>60</v>
@@ -2517,14 +2517,14 @@
       <c r="O20" s="8">
         <v>12.17</v>
       </c>
-      <c r="P20" s="33">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="Q20" s="33">
-        <v>2.16</v>
-      </c>
-      <c r="R20" s="33">
-        <v>1.91</v>
+      <c r="P20" s="26">
+        <v>3.9</v>
+      </c>
+      <c r="Q20" s="26">
+        <v>3.28</v>
+      </c>
+      <c r="R20" s="26">
+        <v>2.54</v>
       </c>
       <c r="S20" s="25" t="s">
         <v>62</v>
@@ -2583,13 +2583,13 @@
       <c r="O21" s="11">
         <v>12</v>
       </c>
-      <c r="P21" s="33">
+      <c r="P21" s="26">
         <v>3.78</v>
       </c>
-      <c r="Q21" s="33">
+      <c r="Q21" s="26">
         <v>3.35</v>
       </c>
-      <c r="R21" s="33">
+      <c r="R21" s="26">
         <v>2.02</v>
       </c>
       <c r="S21" s="25" t="s">
@@ -2651,14 +2651,14 @@
       <c r="O22" s="8">
         <v>6.86</v>
       </c>
-      <c r="P22" s="33">
-        <v>5.07</v>
-      </c>
-      <c r="Q22" s="33">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="R22" s="33">
-        <v>2.74</v>
+      <c r="P22" s="26">
+        <v>4.43</v>
+      </c>
+      <c r="Q22" s="26">
+        <v>4.22</v>
+      </c>
+      <c r="R22" s="26">
+        <v>3.98</v>
       </c>
       <c r="S22" s="25" t="s">
         <v>69</v>
@@ -2717,14 +2717,14 @@
       <c r="O23" s="11">
         <v>10.14</v>
       </c>
-      <c r="P23" s="33">
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="Q23" s="33">
-        <v>4.09</v>
-      </c>
-      <c r="R23" s="33">
-        <v>3.85</v>
+      <c r="P23" s="26">
+        <v>3.55</v>
+      </c>
+      <c r="Q23" s="26">
+        <v>3.08</v>
+      </c>
+      <c r="R23" s="26">
+        <v>2.11</v>
       </c>
       <c r="S23" s="25" t="s">
         <v>58</v>
@@ -2783,14 +2783,14 @@
       <c r="O24" s="8">
         <v>8.14</v>
       </c>
-      <c r="P24" s="33">
-        <v>3.63</v>
-      </c>
-      <c r="Q24" s="33">
-        <v>3.2</v>
-      </c>
-      <c r="R24" s="33">
-        <v>2.8</v>
+      <c r="P24" s="26">
+        <v>3.99</v>
+      </c>
+      <c r="Q24" s="26">
+        <v>3.69</v>
+      </c>
+      <c r="R24" s="26">
+        <v>3.47</v>
       </c>
       <c r="S24" s="25" t="s">
         <v>63</v>
@@ -2849,14 +2849,14 @@
       <c r="O25" s="11">
         <v>11.86</v>
       </c>
-      <c r="P25" s="33">
-        <v>4.67</v>
-      </c>
-      <c r="Q25" s="33">
-        <v>4.03</v>
-      </c>
-      <c r="R25" s="33">
-        <v>2.98</v>
+      <c r="P25" s="26">
+        <v>5.05</v>
+      </c>
+      <c r="Q25" s="26">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="R25" s="26">
+        <v>3.2</v>
       </c>
       <c r="S25" s="25" t="s">
         <v>57</v>
@@ -2915,14 +2915,14 @@
       <c r="O26" s="8">
         <v>5.17</v>
       </c>
-      <c r="P26" s="33">
-        <v>4.67</v>
-      </c>
-      <c r="Q26" s="33">
-        <v>4.03</v>
-      </c>
-      <c r="R26" s="33">
-        <v>2.98</v>
+      <c r="P26" s="26">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="Q26" s="26">
+        <v>4.09</v>
+      </c>
+      <c r="R26" s="26">
+        <v>3.85</v>
       </c>
       <c r="S26" s="25" t="s">
         <v>61</v>
@@ -2981,14 +2981,14 @@
       <c r="O27" s="11">
         <v>5.17</v>
       </c>
-      <c r="P27" s="33">
-        <v>5.2</v>
-      </c>
-      <c r="Q27" s="33">
-        <v>4.66</v>
-      </c>
-      <c r="R27" s="33">
-        <v>4.0999999999999996</v>
+      <c r="P27" s="26">
+        <v>3.69</v>
+      </c>
+      <c r="Q27" s="26">
+        <v>3.37</v>
+      </c>
+      <c r="R27" s="26">
+        <v>2.9</v>
       </c>
       <c r="S27" s="25" t="s">
         <v>60</v>
@@ -3047,14 +3047,14 @@
       <c r="O28" s="8">
         <v>6.47</v>
       </c>
-      <c r="P28" s="33">
-        <v>5.09</v>
-      </c>
-      <c r="Q28" s="33">
-        <v>4.3</v>
-      </c>
-      <c r="R28" s="33">
-        <v>3.6</v>
+      <c r="P28" s="26">
+        <v>3.63</v>
+      </c>
+      <c r="Q28" s="26">
+        <v>3.2</v>
+      </c>
+      <c r="R28" s="26">
+        <v>2.8</v>
       </c>
       <c r="S28" s="25" t="s">
         <v>63</v>
@@ -3113,14 +3113,14 @@
       <c r="O29" s="11">
         <v>5.52</v>
       </c>
-      <c r="P29" s="33">
-        <v>3.63</v>
-      </c>
-      <c r="Q29" s="33">
-        <v>3.49</v>
-      </c>
-      <c r="R29" s="33">
-        <v>3.27</v>
+      <c r="P29" s="26">
+        <v>4.67</v>
+      </c>
+      <c r="Q29" s="26">
+        <v>4.03</v>
+      </c>
+      <c r="R29" s="26">
+        <v>2.98</v>
       </c>
       <c r="S29" s="25" t="s">
         <v>60</v>
@@ -3179,14 +3179,14 @@
       <c r="O30" s="8">
         <v>5.52</v>
       </c>
-      <c r="P30" s="33">
-        <v>3.69</v>
-      </c>
-      <c r="Q30" s="33">
-        <v>3.37</v>
-      </c>
-      <c r="R30" s="33">
-        <v>2.9</v>
+      <c r="P30" s="26">
+        <v>4.67</v>
+      </c>
+      <c r="Q30" s="26">
+        <v>4.03</v>
+      </c>
+      <c r="R30" s="26">
+        <v>2.98</v>
       </c>
       <c r="S30" s="25" t="s">
         <v>57</v>
@@ -3245,14 +3245,14 @@
       <c r="O31" s="11">
         <v>10.67</v>
       </c>
-      <c r="P31" s="33">
-        <v>3.55</v>
-      </c>
-      <c r="Q31" s="33">
-        <v>3.08</v>
-      </c>
-      <c r="R31" s="33">
-        <v>2.11</v>
+      <c r="P31" s="26">
+        <v>5.2</v>
+      </c>
+      <c r="Q31" s="26">
+        <v>4.66</v>
+      </c>
+      <c r="R31" s="26">
+        <v>4.0999999999999996</v>
       </c>
       <c r="S31" s="25" t="s">
         <v>58</v>
@@ -3311,14 +3311,14 @@
       <c r="O32" s="8">
         <v>6.45</v>
       </c>
-      <c r="P32" s="33">
-        <v>5.05</v>
-      </c>
-      <c r="Q32" s="33">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="R32" s="33">
-        <v>3.2</v>
+      <c r="P32" s="26">
+        <v>5.09</v>
+      </c>
+      <c r="Q32" s="26">
+        <v>4.3</v>
+      </c>
+      <c r="R32" s="26">
+        <v>3.6</v>
       </c>
       <c r="S32" s="25" t="s">
         <v>63</v>
@@ -3377,14 +3377,14 @@
       <c r="O33" s="11">
         <v>11.43</v>
       </c>
-      <c r="P33" s="33">
-        <v>3.99</v>
-      </c>
-      <c r="Q33" s="33">
-        <v>3.69</v>
-      </c>
-      <c r="R33" s="33">
-        <v>3.47</v>
+      <c r="P33" s="26">
+        <v>3.63</v>
+      </c>
+      <c r="Q33" s="26">
+        <v>3.49</v>
+      </c>
+      <c r="R33" s="26">
+        <v>3.27</v>
       </c>
       <c r="S33" s="25" t="s">
         <v>58</v>
@@ -3443,14 +3443,14 @@
       <c r="O34" s="8">
         <v>0</v>
       </c>
-      <c r="P34" s="33">
-        <v>4.43</v>
-      </c>
-      <c r="Q34" s="33">
-        <v>4.22</v>
-      </c>
-      <c r="R34" s="33">
-        <v>3.98</v>
+      <c r="P34" s="26">
+        <v>5.07</v>
+      </c>
+      <c r="Q34" s="26">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R34" s="26">
+        <v>2.74</v>
       </c>
       <c r="S34" s="25" t="s">
         <v>63</v>
@@ -3511,13 +3511,13 @@
       <c r="O35" s="11">
         <v>0</v>
       </c>
-      <c r="P35" s="33">
+      <c r="P35" s="26">
         <v>4.28</v>
       </c>
-      <c r="Q35" s="33">
+      <c r="Q35" s="26">
         <v>3.84</v>
       </c>
-      <c r="R35" s="33">
+      <c r="R35" s="26">
         <v>3.08</v>
       </c>
       <c r="S35" s="25" t="s">
@@ -3535,16 +3535,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="P2:R2"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="P2:R2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/학생부우수자_입결.xlsx
+++ b/학생부우수자_입결.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\대진대_입학상담_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04F66A2-4C84-40E0-AD2E-5EDBAECC6DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0005FC-36B9-49B2-867B-D5EEFAE6F025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{333CE5E8-D45C-448F-B07C-A850148192AA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{333CE5E8-D45C-448F-B07C-A850148192AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -923,10 +923,16 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -937,12 +943,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1290,23 +1290,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
       <c r="Q1" t="s">
         <v>73</v>
       </c>
@@ -1321,41 +1321,41 @@
       <c r="C2" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="29" t="s">
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="30" t="s">
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="31" t="s">
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="28" t="s">
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="32" t="s">
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="33" t="s">
+      <c r="T2" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="U2" s="33" t="s">
+      <c r="U2" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="V2" s="33" t="s">
+      <c r="V2" s="28" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1408,10 +1408,10 @@
       <c r="R3" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="S3" s="32"/>
-      <c r="T3" s="33"/>
-      <c r="U3" s="33"/>
-      <c r="V3" s="33"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="20">
@@ -1486,65 +1486,65 @@
         <v>2</v>
       </c>
       <c r="B5" s="9"/>
-      <c r="C5" s="10" t="s">
-        <v>1</v>
+      <c r="C5" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>3.81</v>
+        <v>3.09</v>
       </c>
       <c r="E5" s="3">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="F5" s="2">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="G5" s="4">
-        <v>3.99</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="H5" s="5">
-        <v>3.63</v>
+        <v>3.76</v>
       </c>
       <c r="I5" s="4">
-        <v>3.25</v>
+        <v>2.77</v>
       </c>
       <c r="J5" s="6">
-        <v>3.93</v>
+        <v>3.26</v>
       </c>
       <c r="K5" s="7">
-        <v>3.51</v>
+        <v>2.9</v>
       </c>
       <c r="L5" s="6">
-        <v>2.82</v>
-      </c>
-      <c r="M5" s="11">
-        <v>7.8</v>
-      </c>
-      <c r="N5" s="11">
-        <v>11.33</v>
-      </c>
-      <c r="O5" s="11">
-        <v>6.8</v>
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="M5" s="8">
+        <v>14.8</v>
+      </c>
+      <c r="N5" s="8">
+        <v>16</v>
+      </c>
+      <c r="O5" s="8">
+        <v>9.6</v>
       </c>
       <c r="P5" s="26">
-        <v>3.05</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="Q5" s="26">
-        <v>2.79</v>
+        <v>3.45</v>
       </c>
       <c r="R5" s="26">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="S5" s="25" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="T5" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="U5" s="25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V5" s="25">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1552,65 +1552,65 @@
         <v>3</v>
       </c>
       <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
-        <v>2</v>
+      <c r="C6" s="10" t="s">
+        <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>3.09</v>
+        <v>3.81</v>
       </c>
       <c r="E6" s="3">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="F6" s="2">
+        <v>2.54</v>
+      </c>
+      <c r="G6" s="4">
+        <v>3.99</v>
+      </c>
+      <c r="H6" s="5">
+        <v>3.63</v>
+      </c>
+      <c r="I6" s="4">
+        <v>3.25</v>
+      </c>
+      <c r="J6" s="6">
+        <v>3.93</v>
+      </c>
+      <c r="K6" s="7">
+        <v>3.51</v>
+      </c>
+      <c r="L6" s="6">
+        <v>2.82</v>
+      </c>
+      <c r="M6" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="N6" s="11">
+        <v>11.33</v>
+      </c>
+      <c r="O6" s="11">
+        <v>6.8</v>
+      </c>
+      <c r="P6" s="26">
+        <v>3.05</v>
+      </c>
+      <c r="Q6" s="26">
+        <v>2.79</v>
+      </c>
+      <c r="R6" s="26">
         <v>2.33</v>
       </c>
-      <c r="G6" s="4">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="H6" s="5">
-        <v>3.76</v>
-      </c>
-      <c r="I6" s="4">
-        <v>2.77</v>
-      </c>
-      <c r="J6" s="6">
-        <v>3.26</v>
-      </c>
-      <c r="K6" s="7">
-        <v>2.9</v>
-      </c>
-      <c r="L6" s="6">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="M6" s="8">
-        <v>14.8</v>
-      </c>
-      <c r="N6" s="8">
-        <v>16</v>
-      </c>
-      <c r="O6" s="8">
-        <v>9.6</v>
-      </c>
-      <c r="P6" s="26">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="Q6" s="26">
-        <v>3.45</v>
-      </c>
-      <c r="R6" s="26">
-        <v>2.85</v>
-      </c>
       <c r="S6" s="25" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="T6" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U6" s="25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V6" s="25">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1618,65 +1618,65 @@
         <v>4</v>
       </c>
       <c r="B7" s="9"/>
-      <c r="C7" s="10" t="s">
-        <v>3</v>
+      <c r="C7" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D7" s="2">
-        <v>3.94</v>
+        <v>3.2</v>
       </c>
       <c r="E7" s="3">
-        <v>3.73</v>
+        <v>2.95</v>
       </c>
       <c r="F7" s="2">
-        <v>3.42</v>
+        <v>2.54</v>
       </c>
       <c r="G7" s="4">
-        <v>4.13</v>
+        <v>3.75</v>
       </c>
       <c r="H7" s="5">
-        <v>3.7</v>
+        <v>3.07</v>
       </c>
       <c r="I7" s="4">
-        <v>3.15</v>
+        <v>2.06</v>
       </c>
       <c r="J7" s="6">
-        <v>3.97</v>
+        <v>3.66</v>
       </c>
       <c r="K7" s="7">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="L7" s="6">
-        <v>3.38</v>
-      </c>
-      <c r="M7" s="11">
-        <v>5.33</v>
-      </c>
-      <c r="N7" s="11">
-        <v>6.67</v>
-      </c>
-      <c r="O7" s="11">
-        <v>9.4</v>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M7" s="8">
+        <v>13.33</v>
+      </c>
+      <c r="N7" s="8">
+        <v>11</v>
+      </c>
+      <c r="O7" s="8">
+        <v>14.33</v>
       </c>
       <c r="P7" s="26">
-        <v>4.21</v>
+        <v>3.45</v>
       </c>
       <c r="Q7" s="26">
-        <v>3.94</v>
+        <v>3.07</v>
       </c>
       <c r="R7" s="26">
-        <v>3.52</v>
+        <v>2.74</v>
       </c>
       <c r="S7" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="T7" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="T7" s="25" t="s">
-        <v>66</v>
-      </c>
       <c r="U7" s="25">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V7" s="25">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1684,65 +1684,65 @@
         <v>5</v>
       </c>
       <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
-        <v>49</v>
+      <c r="C8" s="10" t="s">
+        <v>3</v>
       </c>
       <c r="D8" s="2">
-        <v>3.2</v>
+        <v>3.94</v>
       </c>
       <c r="E8" s="3">
-        <v>2.95</v>
+        <v>3.73</v>
       </c>
       <c r="F8" s="2">
-        <v>2.54</v>
+        <v>3.42</v>
       </c>
       <c r="G8" s="4">
-        <v>3.75</v>
+        <v>4.13</v>
       </c>
       <c r="H8" s="5">
-        <v>3.07</v>
+        <v>3.7</v>
       </c>
       <c r="I8" s="4">
-        <v>2.06</v>
+        <v>3.15</v>
       </c>
       <c r="J8" s="6">
-        <v>3.66</v>
+        <v>3.97</v>
       </c>
       <c r="K8" s="7">
-        <v>3.2</v>
+        <v>3.68</v>
       </c>
       <c r="L8" s="6">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="M8" s="8">
-        <v>13.33</v>
-      </c>
-      <c r="N8" s="8">
-        <v>11</v>
-      </c>
-      <c r="O8" s="8">
-        <v>14.33</v>
+        <v>3.38</v>
+      </c>
+      <c r="M8" s="11">
+        <v>5.33</v>
+      </c>
+      <c r="N8" s="11">
+        <v>6.67</v>
+      </c>
+      <c r="O8" s="11">
+        <v>9.4</v>
       </c>
       <c r="P8" s="26">
-        <v>3.45</v>
+        <v>4.21</v>
       </c>
       <c r="Q8" s="26">
-        <v>3.07</v>
+        <v>3.94</v>
       </c>
       <c r="R8" s="26">
-        <v>2.74</v>
+        <v>3.52</v>
       </c>
       <c r="S8" s="25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T8" s="25" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="U8" s="25">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V8" s="25">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1817,58 +1817,58 @@
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2">
-        <v>2.96</v>
+        <v>4.24</v>
       </c>
       <c r="E10" s="3">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="F10" s="2">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="G10" s="4">
-        <v>4.1900000000000004</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H10" s="5">
-        <v>3.59</v>
+        <v>3.88</v>
       </c>
       <c r="I10" s="4">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="J10" s="6">
-        <v>4.03</v>
+        <v>3.57</v>
       </c>
       <c r="K10" s="7">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="L10" s="6">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="M10" s="8">
-        <v>6</v>
+        <v>6.43</v>
       </c>
       <c r="N10" s="8">
-        <v>5.25</v>
+        <v>5.17</v>
       </c>
       <c r="O10" s="8">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="P10" s="26">
-        <v>3.15</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="Q10" s="26">
-        <v>3.1</v>
+        <v>3.93</v>
       </c>
       <c r="R10" s="26">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="S10" s="25" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="T10" s="25" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="U10" s="25">
         <v>4</v>
@@ -1882,65 +1882,65 @@
         <v>8</v>
       </c>
       <c r="B11" s="9"/>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2.96</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2.88</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2.65</v>
+      </c>
+      <c r="G11" s="4">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="H11" s="5">
+        <v>3.59</v>
+      </c>
+      <c r="I11" s="4">
+        <v>3</v>
+      </c>
+      <c r="J11" s="6">
+        <v>4.03</v>
+      </c>
+      <c r="K11" s="7">
+        <v>3.34</v>
+      </c>
+      <c r="L11" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="M11" s="8">
         <v>6</v>
       </c>
-      <c r="D11" s="2">
-        <v>3.85</v>
-      </c>
-      <c r="E11" s="3">
-        <v>3.77</v>
-      </c>
-      <c r="F11" s="2">
-        <v>3.67</v>
-      </c>
-      <c r="G11" s="4">
-        <v>4.09</v>
-      </c>
-      <c r="H11" s="5">
-        <v>3.77</v>
-      </c>
-      <c r="I11" s="4">
-        <v>3.38</v>
-      </c>
-      <c r="J11" s="6">
-        <v>4.21</v>
-      </c>
-      <c r="K11" s="7">
-        <v>3.89</v>
-      </c>
-      <c r="L11" s="6">
-        <v>3.26</v>
-      </c>
-      <c r="M11" s="11">
-        <v>4.33</v>
-      </c>
-      <c r="N11" s="11">
-        <v>8.25</v>
-      </c>
-      <c r="O11" s="11">
-        <v>8.57</v>
+      <c r="N11" s="8">
+        <v>5.25</v>
+      </c>
+      <c r="O11" s="8">
+        <v>6.75</v>
       </c>
       <c r="P11" s="26">
-        <v>3.96</v>
+        <v>3.15</v>
       </c>
       <c r="Q11" s="26">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R11" s="26">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
       <c r="S11" s="25" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="T11" s="25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="U11" s="25">
-        <v>2</v>
-      </c>
-      <c r="V11" s="25" t="s">
-        <v>68</v>
+        <v>4</v>
+      </c>
+      <c r="V11" s="25">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1948,65 +1948,65 @@
         <v>9</v>
       </c>
       <c r="B12" s="1"/>
-      <c r="C12" s="1" t="s">
-        <v>7</v>
+      <c r="C12" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="D12" s="2">
-        <v>4.24</v>
+        <v>3.85</v>
       </c>
       <c r="E12" s="3">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
       <c r="F12" s="2">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="G12" s="4">
-        <v>4.4000000000000004</v>
+        <v>4.09</v>
       </c>
       <c r="H12" s="5">
-        <v>3.88</v>
+        <v>3.77</v>
       </c>
       <c r="I12" s="4">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="J12" s="6">
-        <v>3.57</v>
+        <v>4.21</v>
       </c>
       <c r="K12" s="7">
-        <v>3.23</v>
+        <v>3.89</v>
       </c>
       <c r="L12" s="6">
-        <v>2.54</v>
-      </c>
-      <c r="M12" s="8">
-        <v>6.43</v>
-      </c>
-      <c r="N12" s="8">
-        <v>5.17</v>
-      </c>
-      <c r="O12" s="8">
-        <v>6.25</v>
+        <v>3.26</v>
+      </c>
+      <c r="M12" s="11">
+        <v>4.33</v>
+      </c>
+      <c r="N12" s="11">
+        <v>8.25</v>
+      </c>
+      <c r="O12" s="11">
+        <v>8.57</v>
       </c>
       <c r="P12" s="26">
-        <v>4.5599999999999996</v>
+        <v>3.96</v>
       </c>
       <c r="Q12" s="26">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="R12" s="26">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="S12" s="25" t="s">
         <v>57</v>
       </c>
       <c r="T12" s="25" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="U12" s="25">
-        <v>4</v>
-      </c>
-      <c r="V12" s="25">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="V12" s="25" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2015,64 +2015,64 @@
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2">
+        <v>4.16</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3.93</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3.64</v>
+      </c>
+      <c r="G13" s="4">
+        <v>3.92</v>
+      </c>
+      <c r="H13" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="I13" s="4">
+        <v>3.21</v>
+      </c>
+      <c r="J13" s="6">
+        <v>4.17</v>
+      </c>
+      <c r="K13" s="7">
+        <v>3.7</v>
+      </c>
+      <c r="L13" s="6">
+        <v>2.98</v>
+      </c>
+      <c r="M13" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="N13" s="11">
+        <v>7.4</v>
+      </c>
+      <c r="O13" s="11">
+        <v>10.25</v>
+      </c>
+      <c r="P13" s="26">
+        <v>4.3</v>
+      </c>
+      <c r="Q13" s="26">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="R13" s="26">
         <v>3.95</v>
       </c>
-      <c r="E13" s="3">
-        <v>3.46</v>
-      </c>
-      <c r="F13" s="2">
-        <v>2.98</v>
-      </c>
-      <c r="G13" s="4">
-        <v>4.18</v>
-      </c>
-      <c r="H13" s="5">
-        <v>3.89</v>
-      </c>
-      <c r="I13" s="4">
-        <v>3.35</v>
-      </c>
-      <c r="J13" s="6">
-        <v>4.24</v>
-      </c>
-      <c r="K13" s="7">
-        <v>3.97</v>
-      </c>
-      <c r="L13" s="6">
-        <v>3.27</v>
-      </c>
-      <c r="M13" s="11">
-        <v>6.71</v>
-      </c>
-      <c r="N13" s="11">
-        <v>11.83</v>
-      </c>
-      <c r="O13" s="11">
-        <v>6.63</v>
-      </c>
-      <c r="P13" s="26">
-        <v>4.21</v>
-      </c>
-      <c r="Q13" s="26">
-        <v>3.65</v>
-      </c>
-      <c r="R13" s="26">
-        <v>3.11</v>
-      </c>
       <c r="S13" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T13" s="25" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="U13" s="25">
         <v>3</v>
       </c>
       <c r="V13" s="25">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -2146,65 +2146,65 @@
         <v>12</v>
       </c>
       <c r="B15" s="9"/>
-      <c r="C15" s="10" t="s">
-        <v>10</v>
+      <c r="C15" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="D15" s="2">
-        <v>4.16</v>
+        <v>3.53</v>
       </c>
       <c r="E15" s="3">
-        <v>3.93</v>
+        <v>3.06</v>
       </c>
       <c r="F15" s="2">
-        <v>3.64</v>
+        <v>2.59</v>
       </c>
       <c r="G15" s="4">
-        <v>3.92</v>
+        <v>3.18</v>
       </c>
       <c r="H15" s="5">
-        <v>3.54</v>
+        <v>3.04</v>
       </c>
       <c r="I15" s="4">
-        <v>3.21</v>
+        <v>2.77</v>
       </c>
       <c r="J15" s="6">
-        <v>4.17</v>
+        <v>3.51</v>
       </c>
       <c r="K15" s="7">
-        <v>3.7</v>
+        <v>3.31</v>
       </c>
       <c r="L15" s="6">
-        <v>2.98</v>
-      </c>
-      <c r="M15" s="11">
-        <v>5.75</v>
-      </c>
-      <c r="N15" s="11">
-        <v>7.4</v>
-      </c>
-      <c r="O15" s="11">
-        <v>10.25</v>
+        <v>3.12</v>
+      </c>
+      <c r="M15" s="8">
+        <v>8</v>
+      </c>
+      <c r="N15" s="8">
+        <v>14.57</v>
+      </c>
+      <c r="O15" s="8">
+        <v>15.5</v>
       </c>
       <c r="P15" s="26">
-        <v>4.3</v>
+        <v>3.76</v>
       </c>
       <c r="Q15" s="26">
-        <v>4.1500000000000004</v>
+        <v>3.18</v>
       </c>
       <c r="R15" s="26">
-        <v>3.95</v>
+        <v>2.65</v>
       </c>
       <c r="S15" s="25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T15" s="25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U15" s="25">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="V15" s="25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2212,65 +2212,65 @@
         <v>13</v>
       </c>
       <c r="B16" s="1"/>
-      <c r="C16" s="1" t="s">
-        <v>11</v>
+      <c r="C16" s="10" t="s">
+        <v>8</v>
       </c>
       <c r="D16" s="2">
-        <v>3.53</v>
+        <v>3.95</v>
       </c>
       <c r="E16" s="3">
-        <v>3.06</v>
+        <v>3.46</v>
       </c>
       <c r="F16" s="2">
-        <v>2.59</v>
+        <v>2.98</v>
       </c>
       <c r="G16" s="4">
-        <v>3.18</v>
+        <v>4.18</v>
       </c>
       <c r="H16" s="5">
-        <v>3.04</v>
+        <v>3.89</v>
       </c>
       <c r="I16" s="4">
-        <v>2.77</v>
+        <v>3.35</v>
       </c>
       <c r="J16" s="6">
-        <v>3.51</v>
+        <v>4.24</v>
       </c>
       <c r="K16" s="7">
-        <v>3.31</v>
+        <v>3.97</v>
       </c>
       <c r="L16" s="6">
-        <v>3.12</v>
-      </c>
-      <c r="M16" s="8">
-        <v>8</v>
-      </c>
-      <c r="N16" s="8">
-        <v>14.57</v>
-      </c>
-      <c r="O16" s="8">
-        <v>15.5</v>
+        <v>3.27</v>
+      </c>
+      <c r="M16" s="11">
+        <v>6.71</v>
+      </c>
+      <c r="N16" s="11">
+        <v>11.83</v>
+      </c>
+      <c r="O16" s="11">
+        <v>6.63</v>
       </c>
       <c r="P16" s="26">
-        <v>3.76</v>
+        <v>4.21</v>
       </c>
       <c r="Q16" s="26">
-        <v>3.18</v>
+        <v>3.65</v>
       </c>
       <c r="R16" s="26">
-        <v>2.65</v>
+        <v>3.11</v>
       </c>
       <c r="S16" s="25" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="T16" s="25" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="U16" s="25">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V16" s="25">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2412,65 +2412,65 @@
         <v>16</v>
       </c>
       <c r="B19" s="9"/>
-      <c r="C19" s="10" t="s">
-        <v>14</v>
+      <c r="C19" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="D19" s="2">
-        <v>2.37</v>
+        <v>3.66</v>
       </c>
       <c r="E19" s="3">
-        <v>2.02</v>
+        <v>3.06</v>
       </c>
       <c r="F19" s="2">
-        <v>1.65</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="G19" s="4">
-        <v>2.4300000000000002</v>
+        <v>3.84</v>
       </c>
       <c r="H19" s="5">
-        <v>2.2000000000000002</v>
+        <v>3.45</v>
       </c>
       <c r="I19" s="4">
-        <v>1.84</v>
+        <v>3.07</v>
       </c>
       <c r="J19" s="6">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="K19" s="7">
-        <v>2.29</v>
+        <v>3.19</v>
       </c>
       <c r="L19" s="6">
-        <v>1.57</v>
-      </c>
-      <c r="M19" s="11">
-        <v>12.54</v>
-      </c>
-      <c r="N19" s="11">
-        <v>11.71</v>
-      </c>
-      <c r="O19" s="11">
-        <v>15.32</v>
+        <v>2.84</v>
+      </c>
+      <c r="M19" s="8">
+        <v>10.6</v>
+      </c>
+      <c r="N19" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="O19" s="8">
+        <v>12.17</v>
       </c>
       <c r="P19" s="26">
-        <v>2.4700000000000002</v>
+        <v>3.9</v>
       </c>
       <c r="Q19" s="26">
-        <v>2.16</v>
+        <v>3.28</v>
       </c>
       <c r="R19" s="26">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="S19" s="25" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="T19" s="25" t="s">
         <v>63</v>
       </c>
       <c r="U19" s="25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V19" s="25">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2478,65 +2478,65 @@
         <v>17</v>
       </c>
       <c r="B20" s="1"/>
-      <c r="C20" s="1" t="s">
-        <v>15</v>
+      <c r="C20" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="D20" s="2">
-        <v>3.66</v>
+        <v>2.37</v>
       </c>
       <c r="E20" s="3">
-        <v>3.06</v>
+        <v>2.02</v>
       </c>
       <c r="F20" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="G20" s="4">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="H20" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1.84</v>
+      </c>
+      <c r="J20" s="6">
+        <v>2.76</v>
+      </c>
+      <c r="K20" s="7">
+        <v>2.29</v>
+      </c>
+      <c r="L20" s="6">
+        <v>1.57</v>
+      </c>
+      <c r="M20" s="11">
+        <v>12.54</v>
+      </c>
+      <c r="N20" s="11">
+        <v>11.71</v>
+      </c>
+      <c r="O20" s="11">
+        <v>15.32</v>
+      </c>
+      <c r="P20" s="26">
         <v>2.4700000000000002</v>
       </c>
-      <c r="G20" s="4">
-        <v>3.84</v>
-      </c>
-      <c r="H20" s="5">
-        <v>3.45</v>
-      </c>
-      <c r="I20" s="4">
-        <v>3.07</v>
-      </c>
-      <c r="J20" s="6">
-        <v>3.45</v>
-      </c>
-      <c r="K20" s="7">
-        <v>3.19</v>
-      </c>
-      <c r="L20" s="6">
-        <v>2.84</v>
-      </c>
-      <c r="M20" s="8">
-        <v>10.6</v>
-      </c>
-      <c r="N20" s="8">
-        <v>5.2</v>
-      </c>
-      <c r="O20" s="8">
-        <v>12.17</v>
-      </c>
-      <c r="P20" s="26">
-        <v>3.9</v>
-      </c>
       <c r="Q20" s="26">
-        <v>3.28</v>
+        <v>2.16</v>
       </c>
       <c r="R20" s="26">
-        <v>2.54</v>
+        <v>1.91</v>
       </c>
       <c r="S20" s="25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="T20" s="25" t="s">
         <v>63</v>
       </c>
       <c r="U20" s="25">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V20" s="25">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2613,64 +2613,64 @@
         <v>47</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D22" s="2">
-        <v>4.26</v>
+        <v>4.8</v>
       </c>
       <c r="E22" s="3">
-        <v>4.03</v>
+        <v>4.25</v>
       </c>
       <c r="F22" s="2">
-        <v>3.87</v>
+        <v>2.94</v>
       </c>
       <c r="G22" s="4">
-        <v>5.3</v>
+        <v>4.78</v>
       </c>
       <c r="H22" s="5">
-        <v>4.32</v>
+        <v>4.22</v>
       </c>
       <c r="I22" s="4">
-        <v>3.62</v>
+        <v>3</v>
       </c>
       <c r="J22" s="6">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="K22" s="7">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="L22" s="6">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M22" s="8">
+        <v>4.34</v>
+      </c>
+      <c r="N22" s="8">
+        <v>3.46</v>
+      </c>
+      <c r="O22" s="8">
+        <v>0</v>
+      </c>
+      <c r="P22" s="26">
+        <v>5.07</v>
+      </c>
+      <c r="Q22" s="26">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R22" s="26">
+        <v>2.74</v>
+      </c>
+      <c r="S22" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="T22" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="U22" s="25">
         <v>12</v>
       </c>
-      <c r="N22" s="8">
-        <v>5.7</v>
-      </c>
-      <c r="O22" s="8">
-        <v>6.86</v>
-      </c>
-      <c r="P22" s="26">
-        <v>4.43</v>
-      </c>
-      <c r="Q22" s="26">
-        <v>4.22</v>
-      </c>
-      <c r="R22" s="26">
-        <v>3.98</v>
-      </c>
-      <c r="S22" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="T22" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="U22" s="25">
-        <v>14</v>
-      </c>
       <c r="V22" s="25">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2678,65 +2678,65 @@
         <v>20</v>
       </c>
       <c r="B23" s="9"/>
-      <c r="C23" s="10" t="s">
-        <v>18</v>
+      <c r="C23" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D23" s="2">
-        <v>3.39</v>
+        <v>4.21</v>
       </c>
       <c r="E23" s="3">
-        <v>2.84</v>
+        <v>3.9</v>
       </c>
       <c r="F23" s="2">
-        <v>1.66</v>
+        <v>3.62</v>
       </c>
       <c r="G23" s="4">
-        <v>3.35</v>
+        <v>4.07</v>
       </c>
       <c r="H23" s="5">
-        <v>3.16</v>
+        <v>3.43</v>
       </c>
       <c r="I23" s="4">
-        <v>2.89</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="J23" s="6">
-        <v>3.71</v>
+        <v>4.83</v>
       </c>
       <c r="K23" s="7">
-        <v>3.33</v>
+        <v>4.33</v>
       </c>
       <c r="L23" s="6">
-        <v>2.6</v>
-      </c>
-      <c r="M23" s="11">
-        <v>5.63</v>
-      </c>
-      <c r="N23" s="11">
-        <v>8.6300000000000008</v>
-      </c>
-      <c r="O23" s="11">
-        <v>10.14</v>
+        <v>3.1</v>
+      </c>
+      <c r="M23" s="8">
+        <v>6</v>
+      </c>
+      <c r="N23" s="8">
+        <v>7.63</v>
+      </c>
+      <c r="O23" s="8">
+        <v>5.17</v>
       </c>
       <c r="P23" s="26">
-        <v>3.55</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="Q23" s="26">
-        <v>3.08</v>
+        <v>4.09</v>
       </c>
       <c r="R23" s="26">
-        <v>2.11</v>
+        <v>3.85</v>
       </c>
       <c r="S23" s="25" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="T23" s="25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="U23" s="25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V23" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2744,65 +2744,65 @@
         <v>21</v>
       </c>
       <c r="B24" s="1"/>
-      <c r="C24" s="12" t="s">
-        <v>19</v>
+      <c r="C24" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="D24" s="2">
+        <v>3.43</v>
+      </c>
+      <c r="E24" s="3">
+        <v>3.06</v>
+      </c>
+      <c r="F24" s="2">
+        <v>2.75</v>
+      </c>
+      <c r="G24" s="4">
+        <v>4.42</v>
+      </c>
+      <c r="H24" s="5">
+        <v>3.94</v>
+      </c>
+      <c r="I24" s="4">
+        <v>3.27</v>
+      </c>
+      <c r="J24" s="6">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="K24" s="7">
         <v>3.86</v>
       </c>
-      <c r="E24" s="3">
-        <v>3.61</v>
-      </c>
-      <c r="F24" s="2">
-        <v>3.14</v>
-      </c>
-      <c r="G24" s="4">
-        <v>4.4800000000000004</v>
-      </c>
-      <c r="H24" s="5">
-        <v>3.73</v>
-      </c>
-      <c r="I24" s="4">
+      <c r="L24" s="6">
         <v>2.52</v>
       </c>
-      <c r="J24" s="6">
-        <v>3.8</v>
-      </c>
-      <c r="K24" s="7">
-        <v>3.57</v>
-      </c>
-      <c r="L24" s="6">
-        <v>3.27</v>
-      </c>
       <c r="M24" s="8">
-        <v>5.83</v>
+        <v>9.86</v>
       </c>
       <c r="N24" s="8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O24" s="8">
-        <v>8.14</v>
+        <v>6.47</v>
       </c>
       <c r="P24" s="26">
-        <v>3.99</v>
+        <v>3.63</v>
       </c>
       <c r="Q24" s="26">
-        <v>3.69</v>
+        <v>3.2</v>
       </c>
       <c r="R24" s="26">
-        <v>3.47</v>
+        <v>2.8</v>
       </c>
       <c r="S24" s="25" t="s">
         <v>63</v>
       </c>
       <c r="T24" s="25" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="U24" s="25">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V24" s="25">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2810,65 +2810,65 @@
         <v>22</v>
       </c>
       <c r="B25" s="9"/>
-      <c r="C25" s="10" t="s">
-        <v>20</v>
+      <c r="C25" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="D25" s="2">
-        <v>4.6900000000000004</v>
+        <v>4.38</v>
       </c>
       <c r="E25" s="3">
-        <v>4.07</v>
+        <v>3.92</v>
       </c>
       <c r="F25" s="2">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="G25" s="4">
-        <v>4.53</v>
+        <v>4.59</v>
       </c>
       <c r="H25" s="5">
-        <v>3.91</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="I25" s="4">
-        <v>3.02</v>
+        <v>3.53</v>
       </c>
       <c r="J25" s="6">
-        <v>4.3899999999999997</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="K25" s="7">
-        <v>3.89</v>
+        <v>4.29</v>
       </c>
       <c r="L25" s="6">
-        <v>3.23</v>
-      </c>
-      <c r="M25" s="11">
-        <v>4.7</v>
-      </c>
-      <c r="N25" s="11">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="O25" s="11">
-        <v>11.86</v>
+        <v>3.7</v>
+      </c>
+      <c r="M25" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="N25" s="8">
+        <v>6</v>
+      </c>
+      <c r="O25" s="8">
+        <v>5.52</v>
       </c>
       <c r="P25" s="26">
-        <v>5.05</v>
+        <v>4.67</v>
       </c>
       <c r="Q25" s="26">
-        <v>4.2699999999999996</v>
+        <v>4.03</v>
       </c>
       <c r="R25" s="26">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="S25" s="25" t="s">
         <v>57</v>
       </c>
       <c r="T25" s="25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="U25" s="25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V25" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2876,65 +2876,65 @@
         <v>23</v>
       </c>
       <c r="B26" s="12"/>
-      <c r="C26" s="1" t="s">
-        <v>21</v>
+      <c r="C26" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="D26" s="2">
-        <v>4.21</v>
+        <v>4.38</v>
       </c>
       <c r="E26" s="3">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="F26" s="2">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="G26" s="4">
-        <v>4.07</v>
+        <v>4.59</v>
       </c>
       <c r="H26" s="5">
-        <v>3.43</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="I26" s="4">
-        <v>2.1800000000000002</v>
+        <v>3.53</v>
       </c>
       <c r="J26" s="6">
-        <v>4.83</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="K26" s="7">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="L26" s="6">
-        <v>3.1</v>
-      </c>
-      <c r="M26" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="M26" s="11">
+        <v>3.7</v>
+      </c>
+      <c r="N26" s="11">
         <v>6</v>
       </c>
-      <c r="N26" s="8">
-        <v>7.63</v>
-      </c>
-      <c r="O26" s="8">
-        <v>5.17</v>
+      <c r="O26" s="11">
+        <v>5.52</v>
       </c>
       <c r="P26" s="26">
-        <v>4.3499999999999996</v>
+        <v>4.67</v>
       </c>
       <c r="Q26" s="26">
-        <v>4.09</v>
+        <v>4.03</v>
       </c>
       <c r="R26" s="26">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="S26" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T26" s="25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="U26" s="25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V26" s="25">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2943,64 +2943,64 @@
       </c>
       <c r="B27" s="9"/>
       <c r="C27" s="10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D27" s="2">
-        <v>3.67</v>
+        <v>5.18</v>
       </c>
       <c r="E27" s="3">
-        <v>3.41</v>
+        <v>4.55</v>
       </c>
       <c r="F27" s="2">
-        <v>3.02</v>
+        <v>3.91</v>
       </c>
       <c r="G27" s="4">
-        <v>4.07</v>
+        <v>4.33</v>
       </c>
       <c r="H27" s="5">
-        <v>3.43</v>
+        <v>4.13</v>
       </c>
       <c r="I27" s="4">
-        <v>2.1800000000000002</v>
+        <v>3.81</v>
       </c>
       <c r="J27" s="6">
-        <v>4.83</v>
+        <v>4.68</v>
       </c>
       <c r="K27" s="7">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="L27" s="6">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="M27" s="11">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="N27" s="11">
-        <v>7.63</v>
+        <v>7.2</v>
       </c>
       <c r="O27" s="11">
-        <v>5.17</v>
+        <v>10.67</v>
       </c>
       <c r="P27" s="26">
-        <v>3.69</v>
+        <v>5.2</v>
       </c>
       <c r="Q27" s="26">
-        <v>3.37</v>
+        <v>4.66</v>
       </c>
       <c r="R27" s="26">
-        <v>2.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="S27" s="25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="T27" s="25" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="U27" s="25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V27" s="25">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -3009,64 +3009,64 @@
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D28" s="2">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="E28" s="3">
+        <v>4.12</v>
+      </c>
+      <c r="F28" s="2">
         <v>3.43</v>
       </c>
-      <c r="E28" s="3">
-        <v>3.06</v>
-      </c>
-      <c r="F28" s="2">
-        <v>2.75</v>
-      </c>
       <c r="G28" s="4">
-        <v>4.42</v>
+        <v>3.81</v>
       </c>
       <c r="H28" s="5">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="I28" s="4">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="J28" s="6">
-        <v>4.3499999999999996</v>
+        <v>4.38</v>
       </c>
       <c r="K28" s="7">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="L28" s="6">
-        <v>2.52</v>
+        <v>3.14</v>
       </c>
       <c r="M28" s="8">
-        <v>9.86</v>
+        <v>4</v>
       </c>
       <c r="N28" s="8">
-        <v>9</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="O28" s="8">
-        <v>6.47</v>
+        <v>6.45</v>
       </c>
       <c r="P28" s="26">
-        <v>3.63</v>
+        <v>5.09</v>
       </c>
       <c r="Q28" s="26">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="R28" s="26">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="S28" s="25" t="s">
         <v>63</v>
       </c>
       <c r="T28" s="25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="U28" s="25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V28" s="25">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -3074,65 +3074,65 @@
         <v>26</v>
       </c>
       <c r="B29" s="9"/>
-      <c r="C29" s="10" t="s">
-        <v>24</v>
+      <c r="C29" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="D29" s="2">
-        <v>4.38</v>
+        <v>3.46</v>
       </c>
       <c r="E29" s="3">
-        <v>3.92</v>
+        <v>3.32</v>
       </c>
       <c r="F29" s="2">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="G29" s="4">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="H29" s="5">
-        <v>4.1900000000000004</v>
+        <v>3.61</v>
       </c>
       <c r="I29" s="4">
-        <v>3.53</v>
+        <v>3.2</v>
       </c>
       <c r="J29" s="6">
-        <v>4.7300000000000004</v>
+        <v>4.07</v>
       </c>
       <c r="K29" s="7">
-        <v>4.29</v>
+        <v>3.8</v>
       </c>
       <c r="L29" s="6">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="M29" s="11">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="N29" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O29" s="11">
-        <v>5.52</v>
+        <v>11.43</v>
       </c>
       <c r="P29" s="26">
-        <v>4.67</v>
+        <v>3.63</v>
       </c>
       <c r="Q29" s="26">
-        <v>4.03</v>
+        <v>3.49</v>
       </c>
       <c r="R29" s="26">
-        <v>2.98</v>
+        <v>3.27</v>
       </c>
       <c r="S29" s="25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="T29" s="25" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="U29" s="25">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V29" s="25">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -3140,62 +3140,62 @@
         <v>27</v>
       </c>
       <c r="B30" s="12"/>
-      <c r="C30" s="12" t="s">
-        <v>25</v>
+      <c r="C30" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D30" s="2">
-        <v>4.38</v>
+        <v>3.67</v>
       </c>
       <c r="E30" s="3">
-        <v>3.92</v>
+        <v>3.41</v>
       </c>
       <c r="F30" s="2">
         <v>3.02</v>
       </c>
       <c r="G30" s="4">
-        <v>4.59</v>
+        <v>4.07</v>
       </c>
       <c r="H30" s="5">
-        <v>4.1900000000000004</v>
+        <v>3.43</v>
       </c>
       <c r="I30" s="4">
-        <v>3.53</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="J30" s="6">
-        <v>4.7300000000000004</v>
+        <v>4.83</v>
       </c>
       <c r="K30" s="7">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="L30" s="6">
-        <v>3.7</v>
-      </c>
-      <c r="M30" s="8">
-        <v>3.7</v>
-      </c>
-      <c r="N30" s="8">
-        <v>6</v>
-      </c>
-      <c r="O30" s="8">
-        <v>5.52</v>
+        <v>3.1</v>
+      </c>
+      <c r="M30" s="11">
+        <v>3.67</v>
+      </c>
+      <c r="N30" s="11">
+        <v>7.63</v>
+      </c>
+      <c r="O30" s="11">
+        <v>5.17</v>
       </c>
       <c r="P30" s="26">
-        <v>4.67</v>
+        <v>3.69</v>
       </c>
       <c r="Q30" s="26">
-        <v>4.03</v>
+        <v>3.37</v>
       </c>
       <c r="R30" s="26">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="S30" s="25" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="T30" s="25" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="U30" s="25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V30" s="25">
         <v>1</v>
@@ -3207,64 +3207,64 @@
       </c>
       <c r="B31" s="9"/>
       <c r="C31" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D31" s="2">
-        <v>5.18</v>
+        <v>3.39</v>
       </c>
       <c r="E31" s="3">
-        <v>4.55</v>
+        <v>2.84</v>
       </c>
       <c r="F31" s="2">
-        <v>3.91</v>
+        <v>1.66</v>
       </c>
       <c r="G31" s="4">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="H31" s="5">
-        <v>4.13</v>
+        <v>3.16</v>
       </c>
       <c r="I31" s="4">
-        <v>3.81</v>
+        <v>2.89</v>
       </c>
       <c r="J31" s="6">
-        <v>4.68</v>
+        <v>3.71</v>
       </c>
       <c r="K31" s="7">
-        <v>4.3</v>
+        <v>3.33</v>
       </c>
       <c r="L31" s="6">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="M31" s="11">
-        <v>4</v>
+        <v>5.63</v>
       </c>
       <c r="N31" s="11">
-        <v>7.2</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="O31" s="11">
-        <v>10.67</v>
+        <v>10.14</v>
       </c>
       <c r="P31" s="26">
-        <v>5.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q31" s="26">
-        <v>4.66</v>
+        <v>3.08</v>
       </c>
       <c r="R31" s="26">
-        <v>4.0999999999999996</v>
+        <v>2.11</v>
       </c>
       <c r="S31" s="25" t="s">
         <v>58</v>
       </c>
       <c r="T31" s="25" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="U31" s="25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V31" s="25">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -3272,65 +3272,65 @@
         <v>29</v>
       </c>
       <c r="B32" s="12"/>
-      <c r="C32" s="1" t="s">
-        <v>27</v>
+      <c r="C32" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D32" s="2">
-        <v>4.8899999999999997</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="E32" s="3">
-        <v>4.12</v>
+        <v>4.07</v>
       </c>
       <c r="F32" s="2">
-        <v>3.43</v>
+        <v>3.06</v>
       </c>
       <c r="G32" s="4">
-        <v>3.81</v>
+        <v>4.53</v>
       </c>
       <c r="H32" s="5">
-        <v>3.54</v>
+        <v>3.91</v>
       </c>
       <c r="I32" s="4">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="J32" s="6">
-        <v>4.38</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="K32" s="7">
-        <v>3.84</v>
+        <v>3.89</v>
       </c>
       <c r="L32" s="6">
-        <v>3.14</v>
-      </c>
-      <c r="M32" s="8">
-        <v>4</v>
-      </c>
-      <c r="N32" s="8">
+        <v>3.23</v>
+      </c>
+      <c r="M32" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="N32" s="11">
         <v>4.4000000000000004</v>
       </c>
-      <c r="O32" s="8">
-        <v>6.45</v>
+      <c r="O32" s="11">
+        <v>11.86</v>
       </c>
       <c r="P32" s="26">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="Q32" s="26">
-        <v>4.3</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="R32" s="26">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="S32" s="25" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="T32" s="25" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="U32" s="25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V32" s="25">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -3338,65 +3338,65 @@
         <v>30</v>
       </c>
       <c r="B33" s="9"/>
-      <c r="C33" s="9" t="s">
-        <v>28</v>
+      <c r="C33" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="D33" s="2">
-        <v>3.46</v>
+        <v>3.86</v>
       </c>
       <c r="E33" s="3">
-        <v>3.32</v>
+        <v>3.61</v>
       </c>
       <c r="F33" s="2">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="G33" s="4">
-        <v>3.94</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="H33" s="5">
-        <v>3.61</v>
+        <v>3.73</v>
       </c>
       <c r="I33" s="4">
-        <v>3.2</v>
+        <v>2.52</v>
       </c>
       <c r="J33" s="6">
-        <v>4.07</v>
+        <v>3.8</v>
       </c>
       <c r="K33" s="7">
-        <v>3.8</v>
+        <v>3.57</v>
       </c>
       <c r="L33" s="6">
-        <v>3.52</v>
-      </c>
-      <c r="M33" s="11">
-        <v>8</v>
-      </c>
-      <c r="N33" s="11">
-        <v>7</v>
-      </c>
-      <c r="O33" s="11">
-        <v>11.43</v>
+        <v>3.27</v>
+      </c>
+      <c r="M33" s="8">
+        <v>5.83</v>
+      </c>
+      <c r="N33" s="8">
+        <v>5</v>
+      </c>
+      <c r="O33" s="8">
+        <v>8.14</v>
       </c>
       <c r="P33" s="26">
-        <v>3.63</v>
+        <v>3.99</v>
       </c>
       <c r="Q33" s="26">
-        <v>3.49</v>
+        <v>3.69</v>
       </c>
       <c r="R33" s="26">
-        <v>3.27</v>
+        <v>3.47</v>
       </c>
       <c r="S33" s="25" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="T33" s="25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U33" s="25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V33" s="25">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -3405,64 +3405,64 @@
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D34" s="2">
-        <v>4.8</v>
+        <v>4.26</v>
       </c>
       <c r="E34" s="3">
-        <v>4.25</v>
+        <v>4.03</v>
       </c>
       <c r="F34" s="2">
-        <v>2.94</v>
+        <v>3.87</v>
       </c>
       <c r="G34" s="4">
-        <v>4.78</v>
+        <v>5.3</v>
       </c>
       <c r="H34" s="5">
+        <v>4.32</v>
+      </c>
+      <c r="I34" s="4">
+        <v>3.62</v>
+      </c>
+      <c r="J34" s="6">
+        <v>4.24</v>
+      </c>
+      <c r="K34" s="7">
+        <v>3.99</v>
+      </c>
+      <c r="L34" s="6">
+        <v>3.47</v>
+      </c>
+      <c r="M34" s="8">
+        <v>12</v>
+      </c>
+      <c r="N34" s="8">
+        <v>5.7</v>
+      </c>
+      <c r="O34" s="8">
+        <v>6.86</v>
+      </c>
+      <c r="P34" s="26">
+        <v>4.43</v>
+      </c>
+      <c r="Q34" s="26">
         <v>4.22</v>
       </c>
-      <c r="I34" s="4">
-        <v>3</v>
-      </c>
-      <c r="J34" s="6">
+      <c r="R34" s="26">
+        <v>3.98</v>
+      </c>
+      <c r="S34" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="T34" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="U34" s="25">
+        <v>14</v>
+      </c>
+      <c r="V34" s="25">
         <v>0</v>
-      </c>
-      <c r="K34" s="7">
-        <v>0</v>
-      </c>
-      <c r="L34" s="6">
-        <v>0</v>
-      </c>
-      <c r="M34" s="8">
-        <v>4.34</v>
-      </c>
-      <c r="N34" s="8">
-        <v>3.46</v>
-      </c>
-      <c r="O34" s="8">
-        <v>0</v>
-      </c>
-      <c r="P34" s="26">
-        <v>5.07</v>
-      </c>
-      <c r="Q34" s="26">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="R34" s="26">
-        <v>2.74</v>
-      </c>
-      <c r="S34" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="T34" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="U34" s="25">
-        <v>12</v>
-      </c>
-      <c r="V34" s="25">
-        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3535,16 +3535,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="M2:O2"/>
     <mergeCell ref="S2:S3"/>
     <mergeCell ref="T2:T3"/>
     <mergeCell ref="U2:U3"/>
     <mergeCell ref="V2:V3"/>
     <mergeCell ref="P2:R2"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/학생부우수자_입결.xlsx
+++ b/학생부우수자_입결.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\대진대_입학상담_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0005FC-36B9-49B2-867B-D5EEFAE6F025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359BCE28-8D9B-4C8B-96D4-DBC258AE4625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{333CE5E8-D45C-448F-B07C-A850148192AA}"/>
   </bookViews>
@@ -923,16 +923,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -943,6 +937,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1290,23 +1290,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
       <c r="Q1" t="s">
         <v>73</v>
       </c>
@@ -1321,41 +1321,41 @@
       <c r="C2" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="31" t="s">
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32" t="s">
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="33" t="s">
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="29" t="s">
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="27" t="s">
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="28" t="s">
+      <c r="T2" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="U2" s="28" t="s">
+      <c r="U2" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="V2" s="28" t="s">
+      <c r="V2" s="33" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1408,10 +1408,10 @@
       <c r="R3" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="S3" s="27"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="33"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="33"/>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="20">
@@ -1535,16 +1535,16 @@
         <v>2.85</v>
       </c>
       <c r="S5" s="25" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="T5" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U5" s="25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V5" s="25">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1601,16 +1601,16 @@
         <v>2.33</v>
       </c>
       <c r="S6" s="25" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="T6" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="U6" s="25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V6" s="25">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1667,16 +1667,16 @@
         <v>2.74</v>
       </c>
       <c r="S7" s="25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T7" s="25" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="U7" s="25">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V7" s="25">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1733,16 +1733,16 @@
         <v>3.52</v>
       </c>
       <c r="S8" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="T8" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="T8" s="25" t="s">
-        <v>66</v>
-      </c>
       <c r="U8" s="25">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V8" s="25">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1865,10 +1865,10 @@
         <v>3.3</v>
       </c>
       <c r="S10" s="25" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="T10" s="25" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="U10" s="25">
         <v>4</v>
@@ -1931,16 +1931,16 @@
         <v>3.02</v>
       </c>
       <c r="S11" s="25" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="T11" s="25" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="U11" s="25">
-        <v>4</v>
-      </c>
-      <c r="V11" s="25">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="V11" s="25" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -2000,13 +2000,13 @@
         <v>57</v>
       </c>
       <c r="T12" s="25" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="U12" s="25">
-        <v>2</v>
-      </c>
-      <c r="V12" s="25" t="s">
-        <v>68</v>
+        <v>4</v>
+      </c>
+      <c r="V12" s="25">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2063,16 +2063,16 @@
         <v>3.95</v>
       </c>
       <c r="S13" s="25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T13" s="25" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="U13" s="25">
         <v>3</v>
       </c>
       <c r="V13" s="25">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -2195,16 +2195,16 @@
         <v>2.65</v>
       </c>
       <c r="S15" s="25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T15" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="U15" s="25">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V15" s="25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2261,16 +2261,16 @@
         <v>3.11</v>
       </c>
       <c r="S16" s="25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="T16" s="25" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="U16" s="25">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="V16" s="25">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2461,16 +2461,16 @@
         <v>2.54</v>
       </c>
       <c r="S19" s="25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="T19" s="25" t="s">
         <v>63</v>
       </c>
       <c r="U19" s="25">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V19" s="25">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2527,16 +2527,16 @@
         <v>1.91</v>
       </c>
       <c r="S20" s="25" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="T20" s="25" t="s">
         <v>63</v>
       </c>
       <c r="U20" s="25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V20" s="25">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2661,16 +2661,16 @@
         <v>2.74</v>
       </c>
       <c r="S22" s="25" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="T22" s="25" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="U22" s="25">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V22" s="25">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2727,16 +2727,16 @@
         <v>3.85</v>
       </c>
       <c r="S23" s="25" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="T23" s="25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="U23" s="25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V23" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2796,13 +2796,13 @@
         <v>63</v>
       </c>
       <c r="T24" s="25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="U24" s="25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V24" s="25">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2862,13 +2862,13 @@
         <v>57</v>
       </c>
       <c r="T25" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U25" s="25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V25" s="25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2925,16 +2925,16 @@
         <v>2.98</v>
       </c>
       <c r="S26" s="25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T26" s="25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="U26" s="25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V26" s="25">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2991,16 +2991,16 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="S27" s="25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="T27" s="25" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="U27" s="25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V27" s="25">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -3060,13 +3060,13 @@
         <v>63</v>
       </c>
       <c r="T28" s="25" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="U28" s="25">
+        <v>1</v>
+      </c>
+      <c r="V28" s="25">
         <v>3</v>
-      </c>
-      <c r="V28" s="25">
-        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -3123,16 +3123,16 @@
         <v>3.27</v>
       </c>
       <c r="S29" s="25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="T29" s="25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="U29" s="25">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="V29" s="25">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -3189,13 +3189,13 @@
         <v>2.9</v>
       </c>
       <c r="S30" s="25" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="T30" s="25" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="U30" s="25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V30" s="25">
         <v>1</v>
@@ -3258,13 +3258,13 @@
         <v>58</v>
       </c>
       <c r="T31" s="25" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="U31" s="25">
+        <v>5</v>
+      </c>
+      <c r="V31" s="25">
         <v>3</v>
-      </c>
-      <c r="V31" s="25">
-        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -3321,16 +3321,16 @@
         <v>3.2</v>
       </c>
       <c r="S32" s="25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T32" s="25" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="U32" s="25">
         <v>6</v>
       </c>
       <c r="V32" s="25">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -3387,16 +3387,16 @@
         <v>3.47</v>
       </c>
       <c r="S33" s="25" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="T33" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="U33" s="25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V33" s="25">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -3453,16 +3453,16 @@
         <v>3.98</v>
       </c>
       <c r="S34" s="25" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="T34" s="25" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="U34" s="25">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V34" s="25">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3535,16 +3535,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="P2:R2"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="P2:R2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
